--- a/dataset/Non-Faulty/wrong_arguments_func_pointer.xlsx
+++ b/dataset/Non-Faulty/wrong_arguments_func_pointer.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_011_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_011 () { wrong_arguments_func_pointer_011_s_001 st; void (*fptr)(wrong_arguments_func_pointer_011_s_001*); fptr = wrong_arguments_func_pointer_011_func_001; /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ fptr(&amp;st); fptr = wrong_arguments_func_pointer_011_func_002; fptr(&amp;st); fptr = wrong_arguments_func_pointer_011_func_003; fptr(&amp;st); } void wrong_arguments_func_pointer_011_func_003(wrong_arguments_func_pointer_011_s_001 *st) { st-&gt;b = st-&gt;c; } void wrong_arguments_func_pointer_011_func_002(wrong_arguments_func_pointer_011_s_001 *st) { int temp; int i; for (i = 0; i &lt; MAX; i++) { st-&gt;arr[i] = i; temp = st-&gt;arr[i]; } } void wrong_arguments_func_pointer_011_func_001(wrong_arguments_func_pointer_011_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; }</t>
+          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_011_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_011 () { wrong_arguments_func_pointer_011_s_001 st; void (*fptr)(wrong_arguments_func_pointer_011_s_001*); fptr = wrong_arguments_func_pointer_011_func_001; /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ fptr(&amp;st); fptr = wrong_arguments_func_pointer_011_func_002; fptr(&amp;st); fptr = wrong_arguments_func_pointer_011_func_003; fptr(&amp;st); } void wrong_arguments_func_pointer_011_func_001(wrong_arguments_func_pointer_011_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; } void wrong_arguments_func_pointer_011_func_003(wrong_arguments_func_pointer_011_s_001 *st) { st-&gt;b = st-&gt;c; } void wrong_arguments_func_pointer_011_func_002(wrong_arguments_func_pointer_011_s_001 *st) { int temp; int i; for (i = 0; i &lt; MAX; i++) { st-&gt;arr[i] = i; temp = st-&gt;arr[i]; } }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_012_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_012 () { wrong_arguments_func_pointer_012_s_001 st,*st1; st1 = (wrong_arguments_func_pointer_012_s_001 *)malloc(1*sizeof(wrong_arguments_func_pointer_012_s_001)); void (*fptr)(wrong_arguments_func_pointer_012_s_001*); fptr = wrong_arguments_func_pointer_012_func_001; fptr(&amp;st); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ void (*fptr1)(wrong_arguments_func_pointer_012_s_001,wrong_arguments_func_pointer_012_s_001 *); fptr1 = wrong_arguments_func_pointer_012_func_002; fptr1(st,st1); void (*fptr2)(wrong_arguments_func_pointer_012_s_001 *,int); fptr2 = wrong_arguments_func_pointer_012_func_003; fptr2(&amp;st,1); } void wrong_arguments_func_pointer_012_func_001(wrong_arguments_func_pointer_012_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; } void wrong_arguments_func_pointer_012_func_002(wrong_arguments_func_pointer_012_s_001 st,wrong_arguments_func_pointer_012_s_001* st1) { int temp=0; int i; memset(st1, 0, sizeof(*st1)); for (i = 0; i &lt; MAX; i++) { st.arr[i] = i; st1-&gt;arr[i] = st.arr[i]+i; temp += st.arr[i]; } } void wrong_arguments_func_pointer_012_func_003(wrong_arguments_func_pointer_012_s_001 *st, int a) { st-&gt;b = st-&gt;c+a; }</t>
+          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_012_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_012 () { wrong_arguments_func_pointer_012_s_001 st,*st1; st1 = (wrong_arguments_func_pointer_012_s_001 *)malloc(1*sizeof(wrong_arguments_func_pointer_012_s_001)); void (*fptr)(wrong_arguments_func_pointer_012_s_001*); fptr = wrong_arguments_func_pointer_012_func_001; fptr(&amp;st); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ void (*fptr1)(wrong_arguments_func_pointer_012_s_001,wrong_arguments_func_pointer_012_s_001 *); fptr1 = wrong_arguments_func_pointer_012_func_002; fptr1(st,st1); void (*fptr2)(wrong_arguments_func_pointer_012_s_001 *,int); fptr2 = wrong_arguments_func_pointer_012_func_003; fptr2(&amp;st,1); } void wrong_arguments_func_pointer_012_func_001(wrong_arguments_func_pointer_012_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; } void wrong_arguments_func_pointer_012_func_003(wrong_arguments_func_pointer_012_s_001 *st, int a) { st-&gt;b = st-&gt;c+a; } void wrong_arguments_func_pointer_012_func_002(wrong_arguments_func_pointer_012_s_001 st,wrong_arguments_func_pointer_012_s_001* st1) { int temp=0; int i; memset(st1, 0, sizeof(*st1)); for (i = 0; i &lt; MAX; i++) { st.arr[i] = i; st1-&gt;arr[i] = st.arr[i]+i; temp += st.arr[i]; } }</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_014 () { long arr[5]; if(wrong_arguments_func_pointer_014_func_001(0) == 0) { long (*fptr)(long [],int); long a; fptr = wrong_arguments_func_pointer_014_func_002; a =fptr(arr,5); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } } int wrong_arguments_func_pointer_014_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; } long wrong_arguments_func_pointer_014_func_002 (long a[],int max) { int i; for(i=0;i&lt;max;i++) { a[i] = i; } return a[i]; }</t>
+          <t>char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_014 () { long arr[5]; if(wrong_arguments_func_pointer_014_func_001(0) == 0) { long (*fptr)(long [],int); long a; fptr = wrong_arguments_func_pointer_014_func_002; a =fptr(arr,5); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } } long wrong_arguments_func_pointer_014_func_002 (long a[],int max) { int i; for(i=0;i&lt;max;i++) { a[i] = i; } return a[i]; } int wrong_arguments_func_pointer_014_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,14 +764,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -786,14 +786,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -808,14 +808,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/wrong_arguments_func_pointer.c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_018_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_018 () { wrong_arguments_func_pointer_018_s_001 st,*st1; st1 = (wrong_arguments_func_pointer_018_s_001 *)malloc(1*sizeof(wrong_arguments_func_pointer_018_s_001)); memset(st1, 0, sizeof(*st1)); wrong_arguments_func_pointer_018_fptr_gbl = wrong_arguments_func_pointer_018_func_001; wrong_arguments_func_pointer_018_fptr_gbl(&amp;st); void (*fptr3)(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1); fptr3 = wrong_arguments_func_pointer_018_func_004; fptr3(st,st1); } void wrong_arguments_func_pointer_018_func_001(wrong_arguments_func_pointer_018_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; func_pointer_018_global_set = 1; } void wrong_arguments_func_pointer_018_func_004(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1) { if (func_pointer_018_global_set == MAX) { wrong_arguments_func_pointer_018_fptr1_gbl = wrong_arguments_func_pointer_018_func_002; wrong_arguments_func_pointer_018_fptr1_gbl(st,st1); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } else { wrong_arguments_func_pointer_018_fptr2_gbl = wrong_arguments_func_pointer_018_func_003; wrong_arguments_func_pointer_018_fptr2_gbl(&amp;st,1); } } void wrong_arguments_func_pointer_018_func_002(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { st.arr[i] = i; st1-&gt;arr[i] = st.arr[i]+i; temp += st.arr[i]; } } void wrong_arguments_func_pointer_018_func_003(wrong_arguments_func_pointer_018_s_001 *st, int a) { st-&gt;b = st-&gt;c+a; }</t>
+          <t>#define MAX 10 #define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } wrong_arguments_func_pointer_018_s_001; char **wrong_arguments_func_pointer_015_dst1_gbl=NULL; int func_pointer_018_global_set=0; extern volatile int vflag; void wrong_arguments_func_pointer_018 () { wrong_arguments_func_pointer_018_s_001 st,*st1; st1 = (wrong_arguments_func_pointer_018_s_001 *)malloc(1*sizeof(wrong_arguments_func_pointer_018_s_001)); memset(st1, 0, sizeof(*st1)); wrong_arguments_func_pointer_018_fptr_gbl = wrong_arguments_func_pointer_018_func_001; wrong_arguments_func_pointer_018_fptr_gbl(&amp;st); void (*fptr3)(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1); fptr3 = wrong_arguments_func_pointer_018_func_004; fptr3(st,st1); } void wrong_arguments_func_pointer_018_func_004(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1) { if (func_pointer_018_global_set == MAX) { wrong_arguments_func_pointer_018_fptr1_gbl = wrong_arguments_func_pointer_018_func_002; wrong_arguments_func_pointer_018_fptr1_gbl(st,st1); /*Tool should not detect this line as error*//*No ERROR:Wrong arguments passed to a function pointer*/ } else { wrong_arguments_func_pointer_018_fptr2_gbl = wrong_arguments_func_pointer_018_func_003; wrong_arguments_func_pointer_018_fptr2_gbl(&amp;st,1); } } void wrong_arguments_func_pointer_018_func_003(wrong_arguments_func_pointer_018_s_001 *st, int a) { st-&gt;b = st-&gt;c+a; } void wrong_arguments_func_pointer_018_func_002(wrong_arguments_func_pointer_018_s_001 st,wrong_arguments_func_pointer_018_s_001* st1) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { st.arr[i] = i; st1-&gt;arr[i] = st.arr[i]+i; temp += st.arr[i]; } } void wrong_arguments_func_pointer_018_func_001(wrong_arguments_func_pointer_018_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; func_pointer_018_global_set = 1; }</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
